--- a/02_加值成品/八下/八下1-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下1-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下1-1 化學反應與化學式　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下1-1 化學反應與化學式　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>化學反應中反應物變成？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>水溶液</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>生成物</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>係數</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>轉變</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>反應式箭號左邊是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>反應物</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>重新組合</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>生成物</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>起始</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>反應式箭號右邊是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>水溶液</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>放光放熱變色</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>箭號→</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>生成物</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>化學反應中原子種類？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>固體</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>反應徵象</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>重新組合</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>平衡反應式要使兩邊原子數？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>箭號→</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>相等</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>平衡</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>(aq)表示物質狀態為？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>重新組合</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>水溶液</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>反應物</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>溶於水</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>反應產生沉澱是一種？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>反應徵象</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>生成物</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>放光放熱變色</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>水溶液</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>現象</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>平衡時能改的是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>化學反應式</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>箭號→</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>反應物</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>係數</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>非下標</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>化學反應以什麼式子表示？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>化學反應式</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>放光放熱變色</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>生成物</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>水溶液</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>表示</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>反應物與生成物之間用什麼符號？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>箭號→</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>水溶液</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>箭號</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下1-1 化學反應與化學式　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下1-1 化學反應與化學式　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>2H₂+O₂→2H₂O中水的係數？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>平衡</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>(g)代表什麼狀態？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>反應物</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>氣體</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>gas</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>C+O₂→CO₂是否平衡？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>箭號→</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>質量守恆</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>放光放熱變色</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>兩邊各元素相等</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>反應前後總質量如何？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>反應徵象</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>生成物</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>重新組合</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>氣泡產生代表生成？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>固體</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>氣體</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>放光放熱變色</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>徵象</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>平衡H₂+Cl₂→?HCl,HCl係數？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>2HCl</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>化學反應本質是原子？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>重新組合</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>係數</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>箭號→</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>生成物</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>重排</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>(s)表示？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>固體</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>係數</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>質量守恆</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>放光放熱變色</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>solid</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>平衡2H₂+O₂→2H₂O中O₂係數？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>平衡</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>化學反應中原子總數在反應前後？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>重新組合</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>水溶液</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下1-1 化學反應與化學式　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下1-1 化學反應與化學式　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>平衡 Fe+O₂→Fe₂O₃ 的鐵係數？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>係數</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>4(4Fe+3O₂→2Fe₂O₃)</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>反應徵象</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>配平</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何平衡只能改係數不改下標？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>放光放熱變色</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>改下標會變成不同物質</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>化學式固定</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>反應物3g+反應物5g→生成物?g</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>質量守恆</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>平衡 CH₄+O₂→CO₂+H₂O 的O₂係數？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>CH₄+2O₂→CO₂+2H₂O</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>化學變化與物理變化差別？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>有無新物質生成</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>反應物</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>係數</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>本質</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>鎂帶燃燒變白粉,是何反應徵象？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>放光放熱變色</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>重新組合</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>固體</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>水溶液</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>多重</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>平衡 Al+O₂→Al₂O₃ 的Al係數？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>4Al+3O₂→2Al₂O₃</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>反應式須符合什麼定律才平衡？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>質量守恆</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>箭號→</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>生成物</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>原子守恆</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>平衡N₂+H₂→NH₃的H₂係數？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>N₂+3H₂→2NH₃</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>反應物共10g生成物之一6g另一？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下1-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下1-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>轉變</t>
+          <t>轉變：反應開始的物質叫反應物，經過化學反應後變成新的物質，這就是生成物</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>起始</t>
+          <t>起始：化學反應式的箭號就像「變成」的意思，箭號左邊寫的是還沒反應的原料</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>結果</t>
+          <t>結果：箭號右邊寫的是反應完成後新產生出來的物質</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：反應只是把原子重新排列組合，並不會把某種原子變成另一種原子</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>平衡：因為原子不會憑空消失或增加，所以箭號兩邊同一種原子的數目一定要一樣多</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>溶於水</t>
+          <t>溶於水：aq是英文aqueous的縮寫，代表這個物質已經溶解在水裡面</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>現象</t>
+          <t>現象：沉澱就是溶液中出現不溶解的固體顆粒，是判斷發生化學反應的線索之一</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>非下標</t>
+          <t>非下標：係數是寫在化學式前面的數字，用來調整分子的個數，讓兩邊原子數相等</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>表示</t>
+          <t>表示：用化學式和箭號來描述反應物如何變成生成物的式子，稱為化學反應式</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>箭號</t>
+          <t>箭號：化學反應式中用箭號→連接反應物和生成物，表示反應物經過反應變成右邊的生成物</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>平衡：這個式子裡水前面的數字2就是係數，代表產生了2個水分子</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>gas：g是英文gas的縮寫，表示這個物質在反應中是氣體狀態</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>兩邊各元素相等</t>
+          <t>兩邊各元素相等：左邊有1個碳、2個氧，右邊也是1個碳、2個氧，數目一樣所以已經平衡</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：因為原子沒有消失也沒有增加，只是重新組合，所以反應前後總質量會維持相同</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>徵象</t>
+          <t>徵象：看到液體中冒出小泡泡，通常表示反應中產生了氣體，這是化學反應的常見現象</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>2HCl</t>
+          <t>2HCl：左邊有2個氫原子和2個氯原子，所以右邊要寫成2HCl才能讓兩邊原子數一樣</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>重排</t>
+          <t>重排：化學反應的本質就是原本連接在一起的原子，拆開後用新的方式重新連接</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>solid</t>
+          <t>solid：s是英文solid的縮寫，表示這個物質在反應中是固體狀態</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>平衡：這個式子左右兩邊已經配平，2個H₂需要1個O₂才能生成2個H₂O，兩邊氫、氧原子數都相等</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：化學反應只是原子重新排列組合，原子本身不會消失或增加，所以反應前後原子總數不變</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>配平</t>
+          <t>配平：要讓兩邊鐵和氧原子數相等，最少要用4個鐵、3個氧氣，生成2個三氧化二鐵</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>化學式固定</t>
+          <t>化學式固定：下標代表分子裡原子的個數，一改變就等於變成了另一種完全不同的物質</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>質量守恆</t>
+          <t>質量守恆：因為反應前後原子總數不變，所以生成物的總質量等於兩個反應物質量相加</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>CH₄+2O₂→CO₂+2H₂O</t>
+          <t>CH₄+2O₂→CO₂+2H₂O：右邊共需4個氧原子（CO2的2個加2個水的2個），所以左邊要2個氧氣分子</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>本質</t>
+          <t>本質：物理變化只是形狀狀態改變，化學變化則是原子重新組合，生成了不同性質的新物質</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>多重</t>
+          <t>多重：鎂帶燃燒時同時發出耀眼白光、放出大量熱、又從銀白色變成白色粉末，是多種徵象一起出現</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>4Al+3O₂→2Al₂O₃</t>
+          <t>4Al+3O₂→2Al₂O₃：右邊2個三氧化二鋁共有4個鋁原子，所以左邊鋁的係數要配成4</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>原子守恆</t>
+          <t>原子守恆：因為原子在反應前後種類和數目都不變，所以反應式配平就是在遵守質量守恆定律</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>N₂+3H₂→2NH₃</t>
+          <t>N₂+3H₂→2NH₃：要讓左邊2個氮原子對應右邊2個NH₃,需要6個氫原子,也就是3個H₂,配平後左右氮、氫原子數才會相等</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：根據質量守恆定律，反應前後總質量不變，反應物共10g全部變成生成物，扣掉已知的6g，另一個生成物就是10−6=4克</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下1-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下1-1_三種難度測驗卷.xlsx
@@ -1515,22 +1515,22 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>相等</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>係數</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>4(4Fe+3O₂→2Fe₂O₃)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>反應徵象</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>配平：要讓兩邊鐵和氧原子數相等，最少要用4個鐵、3個氧氣，生成2個三氧化二鐵</t>
+          <t>配平：要讓兩邊鐵和氧原子數相等，配平後為4Fe+3O₂→2Fe₂O₃，最少要用4個鐵、3個氧氣，生成2個三氧化二鐵</t>
         </is>
       </c>
     </row>
@@ -1555,17 +1555,17 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>生成物</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>放光放熱變色</t>
+          <t>反應徵象</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>相等</t>
+          <t>有無新物質生成</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -1680,17 +1680,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>相等</t>
+          <t>反應徵象</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>反應物</t>
+          <t>放光放熱變色</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>係數</t>
+          <t>生成物</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
